--- a/data/article_tables/data2.xlsx
+++ b/data/article_tables/data2.xlsx
@@ -8,24 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\humuser\Documents\avishai\obsidian\data\article_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534DC165-9F59-4BAD-B744-697FBEC2029F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72B25FE-EAF8-407A-A6E1-D84CFE23F921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31860" yWindow="570" windowWidth="21600" windowHeight="11295" tabRatio="697" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="697" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Frahm 2014" sheetId="1" r:id="rId1"/>
-    <sheet name="Carter and Shackley 2007" sheetId="2" r:id="rId2"/>
-    <sheet name="Oddone et al. 1997 " sheetId="3" r:id="rId3"/>
-    <sheet name="Carter et al. 2017" sheetId="4" r:id="rId4"/>
-    <sheet name="Acquafredda et al. 2018" sheetId="5" r:id="rId5"/>
-    <sheet name="Forster and Grave 2012" sheetId="6" r:id="rId6"/>
-    <sheet name="Multiple" sheetId="7" r:id="rId7"/>
-    <sheet name="Carter et al 2013" sheetId="8" r:id="rId8"/>
-    <sheet name="ROSEN et al 2011" sheetId="9" r:id="rId9"/>
-    <sheet name="Yellin and Perlman 1980" sheetId="10" r:id="rId10"/>
-    <sheet name="Carter et al. 2006" sheetId="12" r:id="rId11"/>
-    <sheet name="Yellin and Perlman 1981" sheetId="13" r:id="rId12"/>
-    <sheet name="Binder et al. 2011" sheetId="15" r:id="rId13"/>
+    <sheet name="Carter and Shackley 2007" sheetId="2" r:id="rId1"/>
+    <sheet name="Oddone et al. 1997 " sheetId="3" r:id="rId2"/>
+    <sheet name="Carter et al. 2017" sheetId="4" r:id="rId3"/>
+    <sheet name="Acquafredda et al. 2018" sheetId="5" r:id="rId4"/>
+    <sheet name="Forster and Grave 2012" sheetId="6" r:id="rId5"/>
+    <sheet name="Multiple" sheetId="7" r:id="rId6"/>
+    <sheet name="Carter et al 2013" sheetId="8" r:id="rId7"/>
+    <sheet name="ROSEN et al 2011" sheetId="9" r:id="rId8"/>
+    <sheet name="Yellin and Perlman 1980" sheetId="10" r:id="rId9"/>
+    <sheet name="Carter et al. 2006" sheetId="12" r:id="rId10"/>
+    <sheet name="Yellin and Perlman 1981" sheetId="13" r:id="rId11"/>
+    <sheet name="Binder et al. 2011" sheetId="15" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -3281,243 +3280,2236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>1349</v>
+      </c>
+      <c r="C2">
+        <v>513</v>
+      </c>
+      <c r="D2">
+        <v>10725</v>
+      </c>
+      <c r="E2">
+        <v>47</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <v>36</v>
+      </c>
+      <c r="H2">
+        <v>181</v>
+      </c>
+      <c r="I2">
+        <v>104</v>
+      </c>
+      <c r="J2">
+        <v>16</v>
+      </c>
+      <c r="K2">
+        <v>141</v>
+      </c>
+      <c r="L2">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>0.180592</v>
+      </c>
+      <c r="N2">
+        <v>0.11007</v>
+      </c>
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>1349</v>
+      </c>
+      <c r="C3">
+        <v>556</v>
+      </c>
+      <c r="D3">
+        <v>11009</v>
+      </c>
+      <c r="E3">
+        <v>48</v>
+      </c>
+      <c r="F3">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>28</v>
+      </c>
+      <c r="H3">
+        <v>179</v>
+      </c>
+      <c r="I3">
+        <v>109</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>137</v>
+      </c>
+      <c r="L3">
+        <v>15</v>
+      </c>
+      <c r="M3">
+        <v>0.110957</v>
+      </c>
+      <c r="N3">
+        <v>8.5489999999999997E-2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>1367</v>
+      </c>
+      <c r="C4">
+        <v>639</v>
+      </c>
+      <c r="D4">
+        <v>10330</v>
+      </c>
+      <c r="E4">
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>220</v>
+      </c>
+      <c r="I4">
+        <v>31</v>
+      </c>
+      <c r="J4">
+        <v>20</v>
+      </c>
+      <c r="K4">
+        <v>77</v>
+      </c>
+      <c r="L4">
+        <v>22</v>
+      </c>
+      <c r="M4">
+        <v>0.28569800000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.26123000000000002</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>1028</v>
+      </c>
+      <c r="C5">
+        <v>449</v>
+      </c>
+      <c r="D5">
+        <v>7835</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>184</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>19</v>
+      </c>
+      <c r="K5">
+        <v>77</v>
+      </c>
+      <c r="L5">
+        <v>36</v>
+      </c>
+      <c r="M5">
+        <v>0.46921000000000002</v>
+      </c>
+      <c r="N5">
+        <v>0.23974000000000001</v>
+      </c>
+      <c r="O5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>1242</v>
+      </c>
+      <c r="C6">
+        <v>483</v>
+      </c>
+      <c r="D6">
+        <v>9144</v>
+      </c>
+      <c r="E6">
+        <v>41</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>33</v>
+      </c>
+      <c r="H6">
+        <v>204</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>27</v>
+      </c>
+      <c r="K6">
+        <v>78</v>
+      </c>
+      <c r="L6">
+        <v>23</v>
+      </c>
+      <c r="M6">
+        <v>0.28866799999999998</v>
+      </c>
+      <c r="N6">
+        <v>0.34027000000000002</v>
+      </c>
+      <c r="O6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>1598</v>
+      </c>
+      <c r="C7">
+        <v>668</v>
+      </c>
+      <c r="D7">
+        <v>13711</v>
+      </c>
+      <c r="E7">
+        <v>71</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>205</v>
+      </c>
+      <c r="I7">
+        <v>117</v>
+      </c>
+      <c r="J7">
+        <v>26</v>
+      </c>
+      <c r="K7">
+        <v>148</v>
+      </c>
+      <c r="L7">
+        <v>14</v>
+      </c>
+      <c r="M7">
+        <v>9.7470000000000001E-2</v>
+      </c>
+      <c r="N7">
+        <v>0.17787</v>
+      </c>
+      <c r="O7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>1200</v>
+      </c>
+      <c r="C8">
+        <v>402</v>
+      </c>
+      <c r="D8">
+        <v>9603</v>
+      </c>
+      <c r="E8">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>189</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>89</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>0.36597600000000002</v>
+      </c>
+      <c r="N8">
+        <v>0.17280000000000001</v>
+      </c>
+      <c r="O8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>1064</v>
+      </c>
+      <c r="C9">
+        <v>501</v>
+      </c>
+      <c r="D9">
+        <v>9118</v>
+      </c>
+      <c r="E9">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>26</v>
+      </c>
+      <c r="H9">
+        <v>201</v>
+      </c>
+      <c r="I9">
+        <v>27</v>
+      </c>
+      <c r="J9">
+        <v>27</v>
+      </c>
+      <c r="K9">
+        <v>87</v>
+      </c>
+      <c r="L9">
+        <v>22</v>
+      </c>
+      <c r="M9">
+        <v>0.25709399999999999</v>
+      </c>
+      <c r="N9">
+        <v>0.31597999999999998</v>
+      </c>
+      <c r="O9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>1078</v>
+      </c>
+      <c r="C10">
+        <v>545</v>
+      </c>
+      <c r="D10">
+        <v>10163</v>
+      </c>
+      <c r="E10">
+        <v>43</v>
+      </c>
+      <c r="F10">
+        <v>19</v>
+      </c>
+      <c r="G10">
+        <v>26</v>
+      </c>
+      <c r="H10">
+        <v>209</v>
+      </c>
+      <c r="I10">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>19</v>
+      </c>
+      <c r="K10">
+        <v>88</v>
+      </c>
+      <c r="L10">
+        <v>25</v>
+      </c>
+      <c r="M10">
+        <v>0.28670200000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.21953</v>
+      </c>
+      <c r="O10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>1051</v>
+      </c>
+      <c r="C11">
+        <v>486</v>
+      </c>
+      <c r="D11">
+        <v>8850</v>
+      </c>
+      <c r="E11">
+        <v>31</v>
+      </c>
+      <c r="F11">
+        <v>19</v>
+      </c>
+      <c r="G11">
+        <v>43</v>
+      </c>
+      <c r="H11">
+        <v>203</v>
+      </c>
+      <c r="I11">
+        <v>24</v>
+      </c>
+      <c r="J11">
+        <v>23</v>
+      </c>
+      <c r="K11">
+        <v>83</v>
+      </c>
+      <c r="L11">
+        <v>23</v>
+      </c>
+      <c r="M11">
+        <v>0.27962100000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.27621000000000001</v>
+      </c>
+      <c r="O11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>1344</v>
+      </c>
+      <c r="C12">
+        <v>525</v>
+      </c>
+      <c r="D12">
+        <v>11164</v>
+      </c>
+      <c r="E12">
+        <v>59</v>
+      </c>
+      <c r="F12">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>172</v>
+      </c>
+      <c r="I12">
+        <v>107</v>
+      </c>
+      <c r="J12">
+        <v>18</v>
+      </c>
+      <c r="K12">
+        <v>131</v>
+      </c>
+      <c r="L12">
+        <v>25</v>
+      </c>
+      <c r="M12">
+        <v>0.18801300000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.13589000000000001</v>
+      </c>
+      <c r="O12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>1285</v>
+      </c>
+      <c r="C13">
+        <v>448</v>
+      </c>
+      <c r="D13">
+        <v>10310</v>
+      </c>
+      <c r="E13">
+        <v>48</v>
+      </c>
+      <c r="F13">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>33</v>
+      </c>
+      <c r="H13">
+        <v>166</v>
+      </c>
+      <c r="I13">
+        <v>105</v>
+      </c>
+      <c r="J13">
+        <v>23</v>
+      </c>
+      <c r="K13">
+        <v>133</v>
+      </c>
+      <c r="L13">
+        <v>24</v>
+      </c>
+      <c r="M13">
+        <v>0.18320600000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.17241000000000001</v>
+      </c>
+      <c r="O13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>1067</v>
+      </c>
+      <c r="C14">
+        <v>507</v>
+      </c>
+      <c r="D14">
+        <v>8729</v>
+      </c>
+      <c r="E14">
+        <v>28</v>
+      </c>
+      <c r="F14">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>33</v>
+      </c>
+      <c r="H14">
+        <v>201</v>
+      </c>
+      <c r="I14">
+        <v>26</v>
+      </c>
+      <c r="J14">
+        <v>27</v>
+      </c>
+      <c r="K14">
+        <v>84</v>
+      </c>
+      <c r="L14">
+        <v>18</v>
+      </c>
+      <c r="M14">
+        <v>0.217807</v>
+      </c>
+      <c r="N14">
+        <v>0.32493</v>
+      </c>
+      <c r="O14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>1080</v>
+      </c>
+      <c r="C15">
+        <v>523</v>
+      </c>
+      <c r="D15">
+        <v>8514</v>
+      </c>
+      <c r="E15">
+        <v>31</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>194</v>
+      </c>
+      <c r="I15">
+        <v>28</v>
+      </c>
+      <c r="J15">
+        <v>22</v>
+      </c>
+      <c r="K15">
+        <v>77</v>
+      </c>
+      <c r="L15">
+        <v>15</v>
+      </c>
+      <c r="M15">
+        <v>0.20014299999999999</v>
+      </c>
+      <c r="N15">
+        <v>0.27987000000000001</v>
+      </c>
+      <c r="O15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>1323</v>
+      </c>
+      <c r="C16">
+        <v>625</v>
+      </c>
+      <c r="D16">
+        <v>12079</v>
+      </c>
+      <c r="E16">
+        <v>55</v>
+      </c>
+      <c r="F16">
+        <v>18</v>
+      </c>
+      <c r="G16">
+        <v>38</v>
+      </c>
+      <c r="H16">
+        <v>188</v>
+      </c>
+      <c r="I16">
+        <v>114</v>
+      </c>
+      <c r="J16">
+        <v>27</v>
+      </c>
+      <c r="K16">
+        <v>140</v>
+      </c>
+      <c r="L16">
+        <v>18</v>
+      </c>
+      <c r="M16">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.19184000000000001</v>
+      </c>
+      <c r="O16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>1117</v>
+      </c>
+      <c r="C17">
+        <v>489</v>
+      </c>
+      <c r="D17">
+        <v>9202</v>
+      </c>
+      <c r="E17">
+        <v>35</v>
+      </c>
+      <c r="F17">
+        <v>19</v>
+      </c>
+      <c r="G17">
+        <v>43</v>
+      </c>
+      <c r="H17">
+        <v>208</v>
+      </c>
+      <c r="I17">
+        <v>25</v>
+      </c>
+      <c r="J17">
+        <v>17</v>
+      </c>
+      <c r="K17">
+        <v>74</v>
+      </c>
+      <c r="L17">
+        <v>28</v>
+      </c>
+      <c r="M17">
+        <v>0.37192199999999997</v>
+      </c>
+      <c r="N17">
+        <v>0.22897000000000001</v>
+      </c>
+      <c r="O17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <v>1122</v>
+      </c>
+      <c r="C18">
+        <v>572</v>
+      </c>
+      <c r="D18">
+        <v>10503</v>
+      </c>
+      <c r="E18">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
+      </c>
+      <c r="G18">
+        <v>36</v>
+      </c>
+      <c r="H18">
+        <v>163</v>
+      </c>
+      <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
+        <v>17</v>
+      </c>
+      <c r="K18">
+        <v>139</v>
+      </c>
+      <c r="L18">
+        <v>18</v>
+      </c>
+      <c r="M18">
+        <v>0.13261999999999999</v>
+      </c>
+      <c r="N18">
+        <v>0.1225</v>
+      </c>
+      <c r="O18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19">
+        <v>1077</v>
+      </c>
+      <c r="C19">
+        <v>636</v>
+      </c>
+      <c r="D19">
+        <v>10028</v>
+      </c>
+      <c r="E19">
+        <v>43</v>
+      </c>
+      <c r="F19">
+        <v>21</v>
+      </c>
+      <c r="G19">
+        <v>37</v>
+      </c>
+      <c r="H19">
+        <v>218</v>
+      </c>
+      <c r="I19">
+        <v>27</v>
+      </c>
+      <c r="J19">
+        <v>24</v>
+      </c>
+      <c r="K19">
+        <v>90</v>
+      </c>
+      <c r="L19">
+        <v>29</v>
+      </c>
+      <c r="M19">
+        <v>0.324349</v>
+      </c>
+      <c r="N19">
+        <v>0.26940999999999998</v>
+      </c>
+      <c r="O19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>1076</v>
+      </c>
+      <c r="C20">
+        <v>504</v>
+      </c>
+      <c r="D20">
+        <v>8790</v>
+      </c>
+      <c r="E20">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>19</v>
+      </c>
+      <c r="G20">
+        <v>27</v>
+      </c>
+      <c r="H20">
+        <v>198</v>
+      </c>
+      <c r="I20">
+        <v>21</v>
+      </c>
+      <c r="J20">
+        <v>19</v>
+      </c>
+      <c r="K20">
+        <v>90</v>
+      </c>
+      <c r="L20">
+        <v>27</v>
+      </c>
+      <c r="M20">
+        <v>0.30358200000000002</v>
+      </c>
+      <c r="N20">
+        <v>0.21406</v>
+      </c>
+      <c r="O20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21">
+        <v>1404</v>
+      </c>
+      <c r="C21">
+        <v>654</v>
+      </c>
+      <c r="D21">
+        <v>12974</v>
+      </c>
+      <c r="E21">
+        <v>56</v>
+      </c>
+      <c r="F21">
+        <v>23</v>
+      </c>
+      <c r="G21">
+        <v>23</v>
+      </c>
+      <c r="H21">
+        <v>198</v>
+      </c>
+      <c r="I21">
+        <v>114</v>
+      </c>
+      <c r="J21">
+        <v>17</v>
+      </c>
+      <c r="K21">
+        <v>155</v>
+      </c>
+      <c r="L21">
+        <v>23</v>
+      </c>
+      <c r="M21">
+        <v>0.147928</v>
+      </c>
+      <c r="N21">
+        <v>0.10920000000000001</v>
+      </c>
+      <c r="O21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
+        <v>1282</v>
+      </c>
+      <c r="C22">
+        <v>735</v>
+      </c>
+      <c r="D22">
+        <v>10925</v>
+      </c>
+      <c r="E22">
+        <v>42</v>
+      </c>
+      <c r="F22">
+        <v>26</v>
+      </c>
+      <c r="G22">
+        <v>24</v>
+      </c>
+      <c r="H22">
+        <v>245</v>
+      </c>
+      <c r="I22">
+        <v>21</v>
+      </c>
+      <c r="J22">
+        <v>27</v>
+      </c>
+      <c r="K22">
+        <v>91</v>
+      </c>
+      <c r="L22">
+        <v>29</v>
+      </c>
+      <c r="M22">
+        <v>0.32323200000000002</v>
+      </c>
+      <c r="N22">
+        <v>0.29715000000000003</v>
+      </c>
+      <c r="O22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23">
+        <v>1063</v>
+      </c>
+      <c r="C23">
+        <v>487</v>
+      </c>
+      <c r="D23">
+        <v>8294</v>
+      </c>
+      <c r="E23">
+        <v>27</v>
+      </c>
+      <c r="F23">
+        <v>18</v>
+      </c>
+      <c r="G23">
+        <v>31</v>
+      </c>
+      <c r="H23">
+        <v>193</v>
+      </c>
+      <c r="I23">
+        <v>25</v>
+      </c>
+      <c r="J23">
+        <v>22</v>
+      </c>
+      <c r="K23">
+        <v>81</v>
+      </c>
+      <c r="L23">
+        <v>20</v>
+      </c>
+      <c r="M23">
+        <v>0.24251500000000001</v>
+      </c>
+      <c r="N23">
+        <v>0.2651</v>
+      </c>
+      <c r="O23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24">
+        <v>1095</v>
+      </c>
+      <c r="C24">
+        <v>456</v>
+      </c>
+      <c r="D24">
+        <v>8408</v>
+      </c>
+      <c r="E24">
+        <v>28</v>
+      </c>
+      <c r="F24">
+        <v>18</v>
+      </c>
+      <c r="G24">
+        <v>23</v>
+      </c>
+      <c r="H24">
+        <v>199</v>
+      </c>
+      <c r="I24">
+        <v>17</v>
+      </c>
+      <c r="J24">
+        <v>23</v>
+      </c>
+      <c r="K24">
+        <v>73</v>
+      </c>
+      <c r="L24">
+        <v>26</v>
+      </c>
+      <c r="M24">
+        <v>0.36020400000000002</v>
+      </c>
+      <c r="N24">
+        <v>0.30947999999999998</v>
+      </c>
+      <c r="O24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25">
+        <v>1191</v>
+      </c>
+      <c r="C25">
+        <v>588</v>
+      </c>
+      <c r="D25">
+        <v>10166</v>
+      </c>
+      <c r="E25">
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>26</v>
+      </c>
+      <c r="G25">
+        <v>28</v>
+      </c>
+      <c r="H25">
+        <v>233</v>
+      </c>
+      <c r="I25">
+        <v>28</v>
+      </c>
+      <c r="J25">
+        <v>24</v>
+      </c>
+      <c r="K25">
+        <v>92</v>
+      </c>
+      <c r="L25">
+        <v>24</v>
+      </c>
+      <c r="M25">
+        <v>0.265158</v>
+      </c>
+      <c r="N25">
+        <v>0.25802999999999998</v>
+      </c>
+      <c r="O25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26">
+        <v>1286</v>
+      </c>
+      <c r="C26">
+        <v>462</v>
+      </c>
+      <c r="D26">
+        <v>8652</v>
+      </c>
+      <c r="E26">
+        <v>40</v>
+      </c>
+      <c r="F26">
+        <v>22</v>
+      </c>
+      <c r="G26">
+        <v>30</v>
+      </c>
+      <c r="H26">
+        <v>191</v>
+      </c>
+      <c r="I26">
+        <v>25</v>
+      </c>
+      <c r="J26">
+        <v>27</v>
+      </c>
+      <c r="K26">
+        <v>78</v>
+      </c>
+      <c r="L26">
+        <v>12</v>
+      </c>
+      <c r="M26">
+        <v>0.155027</v>
+      </c>
+      <c r="N26">
+        <v>0.34092</v>
+      </c>
+      <c r="O26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27">
+        <v>1085</v>
+      </c>
+      <c r="C27">
+        <v>533</v>
+      </c>
+      <c r="D27">
+        <v>8930</v>
+      </c>
+      <c r="E27">
+        <v>36</v>
+      </c>
+      <c r="F27">
+        <v>21</v>
+      </c>
+      <c r="G27">
+        <v>30</v>
+      </c>
+      <c r="H27">
+        <v>192</v>
+      </c>
+      <c r="I27">
+        <v>27</v>
+      </c>
+      <c r="J27">
+        <v>24</v>
+      </c>
+      <c r="K27">
+        <v>89</v>
+      </c>
+      <c r="L27">
+        <v>20</v>
+      </c>
+      <c r="M27">
+        <v>0.230132</v>
+      </c>
+      <c r="N27">
+        <v>0.26972000000000002</v>
+      </c>
+      <c r="O27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28">
+        <v>1296</v>
+      </c>
+      <c r="C28">
+        <v>532</v>
+      </c>
+      <c r="D28">
+        <v>10620</v>
+      </c>
+      <c r="E28">
+        <v>52</v>
+      </c>
+      <c r="F28">
+        <v>18</v>
+      </c>
+      <c r="G28">
+        <v>14</v>
+      </c>
+      <c r="H28">
+        <v>156</v>
+      </c>
+      <c r="I28">
+        <v>107</v>
+      </c>
+      <c r="J28">
+        <v>18</v>
+      </c>
+      <c r="K28">
+        <v>126</v>
+      </c>
+      <c r="L28">
+        <v>16</v>
+      </c>
+      <c r="M28">
+        <v>0.123298</v>
+      </c>
+      <c r="N28">
+        <v>0.13943</v>
+      </c>
+      <c r="O28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29">
+        <v>1422</v>
+      </c>
+      <c r="C29">
+        <v>517</v>
+      </c>
+      <c r="D29">
+        <v>12226</v>
+      </c>
+      <c r="E29">
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>35</v>
+      </c>
+      <c r="H29">
+        <v>185</v>
+      </c>
+      <c r="I29">
+        <v>120</v>
+      </c>
+      <c r="J29">
+        <v>16</v>
+      </c>
+      <c r="K29">
+        <v>140</v>
+      </c>
+      <c r="L29">
+        <v>9</v>
+      </c>
+      <c r="M29">
+        <v>6.0914000000000003E-2</v>
+      </c>
+      <c r="N29">
+        <v>0.11136</v>
+      </c>
+      <c r="O29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30">
+        <v>1239</v>
+      </c>
+      <c r="C30">
+        <v>486</v>
+      </c>
+      <c r="D30">
+        <v>10570</v>
+      </c>
+      <c r="E30">
+        <v>46</v>
+      </c>
+      <c r="F30">
+        <v>16</v>
+      </c>
+      <c r="G30">
+        <v>46</v>
+      </c>
+      <c r="H30">
+        <v>162</v>
+      </c>
+      <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
+        <v>17</v>
+      </c>
+      <c r="K30">
+        <v>127</v>
+      </c>
+      <c r="L30">
+        <v>17</v>
+      </c>
+      <c r="M30">
+        <v>0.132717</v>
+      </c>
+      <c r="N30">
+        <v>0.1338</v>
+      </c>
+      <c r="O30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31">
+        <v>1760</v>
+      </c>
+      <c r="C31">
+        <v>518</v>
+      </c>
+      <c r="D31">
+        <v>10817</v>
+      </c>
+      <c r="E31">
+        <v>46</v>
+      </c>
+      <c r="F31">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>39</v>
+      </c>
+      <c r="H31">
+        <v>173</v>
+      </c>
+      <c r="I31">
+        <v>106</v>
+      </c>
+      <c r="J31">
+        <v>14</v>
+      </c>
+      <c r="K31">
+        <v>134</v>
+      </c>
+      <c r="L31">
+        <v>20</v>
+      </c>
+      <c r="M31">
+        <v>0.14706900000000001</v>
+      </c>
+      <c r="N31">
+        <v>0.1028</v>
+      </c>
+      <c r="O31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32">
+        <v>1051</v>
+      </c>
+      <c r="C32">
+        <v>541</v>
+      </c>
+      <c r="D32">
+        <v>9101</v>
+      </c>
+      <c r="E32">
+        <v>36</v>
+      </c>
+      <c r="F32">
+        <v>20</v>
+      </c>
+      <c r="G32">
+        <v>14</v>
+      </c>
+      <c r="H32">
+        <v>199</v>
+      </c>
+      <c r="I32">
+        <v>27</v>
+      </c>
+      <c r="J32">
+        <v>22</v>
+      </c>
+      <c r="K32">
+        <v>92</v>
+      </c>
+      <c r="L32">
+        <v>20</v>
+      </c>
+      <c r="M32">
+        <v>0.21924099999999999</v>
+      </c>
+      <c r="N32">
+        <v>0.23776</v>
+      </c>
+      <c r="O32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33">
+        <v>1227</v>
+      </c>
+      <c r="C33">
+        <v>454</v>
+      </c>
+      <c r="D33">
+        <v>10121</v>
+      </c>
+      <c r="E33">
+        <v>39</v>
+      </c>
+      <c r="F33">
+        <v>18</v>
+      </c>
+      <c r="G33">
+        <v>28</v>
+      </c>
+      <c r="H33">
+        <v>158</v>
+      </c>
+      <c r="I33">
+        <v>101</v>
+      </c>
+      <c r="J33">
+        <v>15</v>
+      </c>
+      <c r="K33">
+        <v>137</v>
+      </c>
+      <c r="L33">
+        <v>26</v>
+      </c>
+      <c r="M33">
+        <v>0.19034499999999999</v>
+      </c>
+      <c r="N33">
+        <v>0.1099</v>
+      </c>
+      <c r="O33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34">
+        <v>1308</v>
+      </c>
+      <c r="C34">
+        <v>537</v>
+      </c>
+      <c r="D34">
+        <v>11315</v>
+      </c>
+      <c r="E34">
+        <v>47</v>
+      </c>
+      <c r="F34">
+        <v>22</v>
+      </c>
+      <c r="G34">
+        <v>30</v>
+      </c>
+      <c r="H34">
+        <v>169</v>
+      </c>
+      <c r="I34">
+        <v>115</v>
+      </c>
+      <c r="J34">
+        <v>24</v>
+      </c>
+      <c r="K34">
+        <v>139</v>
+      </c>
+      <c r="L34">
+        <v>19</v>
+      </c>
+      <c r="M34">
+        <v>0.13414999999999999</v>
+      </c>
+      <c r="N34">
+        <v>0.16905000000000001</v>
+      </c>
+      <c r="O34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35">
+        <v>1073</v>
+      </c>
+      <c r="C35">
+        <v>443</v>
+      </c>
+      <c r="D35">
+        <v>8427</v>
+      </c>
+      <c r="E35">
+        <v>25</v>
+      </c>
+      <c r="F35">
+        <v>13</v>
+      </c>
+      <c r="G35">
+        <v>26</v>
+      </c>
+      <c r="H35">
+        <v>203</v>
+      </c>
+      <c r="I35">
+        <v>25</v>
+      </c>
+      <c r="J35">
+        <v>13</v>
+      </c>
+      <c r="K35">
+        <v>79</v>
+      </c>
+      <c r="L35">
+        <v>35</v>
+      </c>
+      <c r="M35">
+        <v>0.44720199999999999</v>
+      </c>
+      <c r="N35">
+        <v>0.16594999999999999</v>
+      </c>
+      <c r="O35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36">
+        <v>1095</v>
+      </c>
+      <c r="C36">
+        <v>495</v>
+      </c>
+      <c r="D36">
+        <v>8768</v>
+      </c>
+      <c r="E36">
+        <v>34</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>34</v>
+      </c>
+      <c r="H36">
+        <v>215</v>
+      </c>
+      <c r="I36">
+        <v>20</v>
+      </c>
+      <c r="J36">
+        <v>25</v>
+      </c>
+      <c r="K36">
+        <v>75</v>
+      </c>
+      <c r="L36">
+        <v>28</v>
+      </c>
+      <c r="M36">
+        <v>0.37734299999999998</v>
+      </c>
+      <c r="N36">
+        <v>0.32945999999999998</v>
+      </c>
+      <c r="O36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37">
+        <v>1232</v>
+      </c>
+      <c r="C37">
+        <v>527</v>
+      </c>
+      <c r="D37">
+        <v>10839</v>
+      </c>
+      <c r="E37">
+        <v>49</v>
+      </c>
+      <c r="F37">
+        <v>19</v>
+      </c>
+      <c r="G37">
+        <v>37</v>
+      </c>
+      <c r="H37">
+        <v>176</v>
+      </c>
+      <c r="I37">
+        <v>109</v>
+      </c>
+      <c r="J37">
+        <v>18</v>
+      </c>
+      <c r="K37">
+        <v>132</v>
+      </c>
+      <c r="L37">
+        <v>22</v>
+      </c>
+      <c r="M37">
+        <v>0.16368099999999999</v>
+      </c>
+      <c r="N37">
+        <v>0.13274</v>
+      </c>
+      <c r="O37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38">
+        <v>1231</v>
+      </c>
+      <c r="C38">
+        <v>465</v>
+      </c>
+      <c r="D38">
+        <v>10331</v>
+      </c>
+      <c r="E38">
+        <v>57</v>
+      </c>
+      <c r="F38">
+        <v>13</v>
+      </c>
+      <c r="G38">
+        <v>24</v>
+      </c>
+      <c r="H38">
+        <v>167</v>
+      </c>
+      <c r="I38">
+        <v>99</v>
+      </c>
+      <c r="J38">
+        <v>19</v>
+      </c>
+      <c r="K38">
+        <v>140</v>
+      </c>
+      <c r="L38">
+        <v>20</v>
+      </c>
+      <c r="M38">
+        <v>0.14396500000000001</v>
+      </c>
+      <c r="N38">
+        <v>0.13397000000000001</v>
+      </c>
+      <c r="O38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39">
+        <v>1190</v>
+      </c>
+      <c r="C39">
+        <v>543</v>
+      </c>
+      <c r="D39">
+        <v>9368</v>
+      </c>
+      <c r="E39">
+        <v>39</v>
+      </c>
+      <c r="F39">
+        <v>25</v>
+      </c>
+      <c r="G39">
+        <v>39</v>
+      </c>
+      <c r="H39">
+        <v>226</v>
+      </c>
+      <c r="I39">
+        <v>22</v>
+      </c>
+      <c r="J39">
+        <v>16</v>
+      </c>
+      <c r="K39">
+        <v>85</v>
+      </c>
+      <c r="L39">
+        <v>29</v>
+      </c>
+      <c r="M39">
+        <v>0.34019300000000002</v>
+      </c>
+      <c r="N39">
+        <v>0.19147</v>
+      </c>
+      <c r="O39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40">
+        <v>1433</v>
+      </c>
+      <c r="C40">
+        <v>501</v>
+      </c>
+      <c r="D40">
+        <v>10160</v>
+      </c>
+      <c r="E40">
+        <v>55</v>
+      </c>
+      <c r="F40">
+        <v>19</v>
+      </c>
+      <c r="G40">
+        <v>28</v>
+      </c>
+      <c r="H40">
+        <v>159</v>
+      </c>
+      <c r="I40">
+        <v>104</v>
+      </c>
+      <c r="J40">
+        <v>23</v>
+      </c>
+      <c r="K40">
+        <v>129</v>
+      </c>
+      <c r="L40">
+        <v>20</v>
+      </c>
+      <c r="M40">
+        <v>0.15903600000000001</v>
+      </c>
+      <c r="N40">
+        <v>0.17838999999999999</v>
+      </c>
+      <c r="O40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41">
+        <v>1025</v>
+      </c>
+      <c r="C41">
+        <v>416</v>
+      </c>
+      <c r="D41">
+        <v>7334</v>
+      </c>
+      <c r="E41">
+        <v>29</v>
+      </c>
+      <c r="F41">
+        <v>13</v>
+      </c>
+      <c r="G41">
+        <v>29</v>
+      </c>
+      <c r="H41">
+        <v>167</v>
+      </c>
+      <c r="I41">
+        <v>18</v>
+      </c>
+      <c r="J41">
+        <v>19</v>
+      </c>
+      <c r="K41">
+        <v>77</v>
+      </c>
+      <c r="L41">
+        <v>17</v>
+      </c>
+      <c r="M41">
+        <v>0.222825</v>
+      </c>
+      <c r="N41">
+        <v>0.24248</v>
+      </c>
+      <c r="O41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42">
+        <v>1058</v>
+      </c>
+      <c r="C42">
+        <v>524</v>
+      </c>
+      <c r="D42">
+        <v>8624</v>
+      </c>
+      <c r="E42">
+        <v>29</v>
+      </c>
+      <c r="F42">
+        <v>19</v>
+      </c>
+      <c r="G42">
+        <v>41</v>
+      </c>
+      <c r="H42">
+        <v>202</v>
+      </c>
+      <c r="I42">
+        <v>25</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+      <c r="K42">
+        <v>85</v>
+      </c>
+      <c r="L42">
+        <v>27</v>
+      </c>
+      <c r="M42">
+        <v>0.318913</v>
+      </c>
+      <c r="N42">
+        <v>0.24056</v>
+      </c>
+      <c r="O42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43">
+        <v>1036</v>
+      </c>
+      <c r="C43">
+        <v>472</v>
+      </c>
+      <c r="D43">
+        <v>8644</v>
+      </c>
+      <c r="E43">
+        <v>43</v>
+      </c>
+      <c r="F43">
+        <v>15</v>
+      </c>
+      <c r="G43">
+        <v>36</v>
+      </c>
+      <c r="H43">
+        <v>201</v>
+      </c>
+      <c r="I43">
+        <v>23</v>
+      </c>
+      <c r="J43">
+        <v>19</v>
+      </c>
+      <c r="K43">
+        <v>80</v>
+      </c>
+      <c r="L43">
+        <v>23</v>
+      </c>
+      <c r="M43">
+        <v>0.28834599999999999</v>
+      </c>
+      <c r="N43">
+        <v>0.24192</v>
+      </c>
+      <c r="O43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" t="s">
+        <v>63</v>
+      </c>
+      <c r="F48" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" t="s">
+        <v>65</v>
+      </c>
+      <c r="H48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50">
+        <v>25</v>
+      </c>
+      <c r="D50">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51">
+        <v>9000</v>
+      </c>
+      <c r="D51">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53">
+        <v>510</v>
+      </c>
+      <c r="D53">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54">
+        <v>24</v>
+      </c>
+      <c r="D54">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55">
+        <v>204</v>
+      </c>
+      <c r="D55">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56">
+        <v>24</v>
+      </c>
+      <c r="D56">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57">
+        <v>30</v>
+      </c>
+      <c r="D57">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58">
+        <v>1120</v>
+      </c>
+      <c r="D58">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59">
+        <v>22</v>
+      </c>
+      <c r="D59">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60">
+        <v>35</v>
+      </c>
+      <c r="D60">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61">
+        <v>83</v>
+      </c>
+      <c r="D61">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>899</v>
-      </c>
-      <c r="C1" t="s">
-        <v>900</v>
-      </c>
-      <c r="D1" t="s">
-        <v>901</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>902</v>
-      </c>
-      <c r="B2">
-        <v>23</v>
-      </c>
-      <c r="C2">
-        <v>22.9</v>
-      </c>
-      <c r="D2">
-        <v>22.9</v>
-      </c>
-      <c r="E2">
-        <v>39.299999999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>903</v>
-      </c>
-      <c r="B3">
-        <v>0.159</v>
-      </c>
-      <c r="C3">
-        <v>0.16</v>
-      </c>
-      <c r="D3">
-        <v>0.16</v>
-      </c>
-      <c r="E3">
-        <v>0.54500000000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>904</v>
-      </c>
-      <c r="B4">
-        <v>2.35</v>
-      </c>
-      <c r="C4">
-        <v>2.34</v>
-      </c>
-      <c r="D4">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="E4">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>905</v>
-      </c>
-      <c r="B5">
-        <v>1.96</v>
-      </c>
-      <c r="C5">
-        <v>1.94</v>
-      </c>
-      <c r="D5">
-        <v>1.97</v>
-      </c>
-      <c r="E5">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>906</v>
-      </c>
-      <c r="B6">
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="C6">
-        <v>0.60699999999999998</v>
-      </c>
-      <c r="D6">
-        <v>0.60699999999999998</v>
-      </c>
-      <c r="E6">
-        <v>0.88400000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>907</v>
-      </c>
-      <c r="B7">
-        <v>3.19</v>
-      </c>
-      <c r="C7">
-        <v>3.2</v>
-      </c>
-      <c r="D7">
-        <v>3.22</v>
-      </c>
-      <c r="E7">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>908</v>
-      </c>
-      <c r="B8">
-        <v>23.2</v>
-      </c>
-      <c r="C8">
-        <v>22.4</v>
-      </c>
-      <c r="D8">
-        <v>22.9</v>
-      </c>
-      <c r="E8">
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>909</v>
-      </c>
-      <c r="B9">
-        <v>7.69</v>
-      </c>
-      <c r="C9">
-        <v>7.76</v>
-      </c>
-      <c r="D9">
-        <v>7.76</v>
-      </c>
-      <c r="E9">
-        <v>6.84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>910</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>2.93</v>
-      </c>
-      <c r="D10">
-        <v>2.99</v>
-      </c>
-      <c r="E10">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>911</v>
-      </c>
-      <c r="B11">
-        <v>7.95</v>
-      </c>
-      <c r="C11">
-        <v>7.78</v>
-      </c>
-      <c r="D11">
-        <v>7.97</v>
-      </c>
-      <c r="E11">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>912</v>
-      </c>
-      <c r="B12">
-        <v>1.96</v>
-      </c>
-      <c r="C12">
-        <v>1.96</v>
-      </c>
-      <c r="D12">
-        <v>1.91</v>
-      </c>
-      <c r="E12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>913</v>
-      </c>
-      <c r="B13">
-        <v>159</v>
-      </c>
-      <c r="C13">
-        <v>152</v>
-      </c>
-      <c r="D13">
-        <v>160</v>
-      </c>
-      <c r="E13">
-        <v>550</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="BV1:DE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14713,7 +16705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14995,7 +16987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15762,2236 +17754,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2">
-        <v>1349</v>
-      </c>
-      <c r="C2">
-        <v>513</v>
-      </c>
-      <c r="D2">
-        <v>10725</v>
-      </c>
-      <c r="E2">
-        <v>47</v>
-      </c>
-      <c r="F2">
-        <v>16</v>
-      </c>
-      <c r="G2">
-        <v>36</v>
-      </c>
-      <c r="H2">
-        <v>181</v>
-      </c>
-      <c r="I2">
-        <v>104</v>
-      </c>
-      <c r="J2">
-        <v>16</v>
-      </c>
-      <c r="K2">
-        <v>141</v>
-      </c>
-      <c r="L2">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>0.180592</v>
-      </c>
-      <c r="N2">
-        <v>0.11007</v>
-      </c>
-      <c r="O2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>1349</v>
-      </c>
-      <c r="C3">
-        <v>556</v>
-      </c>
-      <c r="D3">
-        <v>11009</v>
-      </c>
-      <c r="E3">
-        <v>48</v>
-      </c>
-      <c r="F3">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>28</v>
-      </c>
-      <c r="H3">
-        <v>179</v>
-      </c>
-      <c r="I3">
-        <v>109</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>137</v>
-      </c>
-      <c r="L3">
-        <v>15</v>
-      </c>
-      <c r="M3">
-        <v>0.110957</v>
-      </c>
-      <c r="N3">
-        <v>8.5489999999999997E-2</v>
-      </c>
-      <c r="O3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
-        <v>1367</v>
-      </c>
-      <c r="C4">
-        <v>639</v>
-      </c>
-      <c r="D4">
-        <v>10330</v>
-      </c>
-      <c r="E4">
-        <v>44</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4">
-        <v>22</v>
-      </c>
-      <c r="H4">
-        <v>220</v>
-      </c>
-      <c r="I4">
-        <v>31</v>
-      </c>
-      <c r="J4">
-        <v>20</v>
-      </c>
-      <c r="K4">
-        <v>77</v>
-      </c>
-      <c r="L4">
-        <v>22</v>
-      </c>
-      <c r="M4">
-        <v>0.28569800000000001</v>
-      </c>
-      <c r="N4">
-        <v>0.26123000000000002</v>
-      </c>
-      <c r="O4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
-        <v>1028</v>
-      </c>
-      <c r="C5">
-        <v>449</v>
-      </c>
-      <c r="D5">
-        <v>7835</v>
-      </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>184</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>77</v>
-      </c>
-      <c r="L5">
-        <v>36</v>
-      </c>
-      <c r="M5">
-        <v>0.46921000000000002</v>
-      </c>
-      <c r="N5">
-        <v>0.23974000000000001</v>
-      </c>
-      <c r="O5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
-        <v>1242</v>
-      </c>
-      <c r="C6">
-        <v>483</v>
-      </c>
-      <c r="D6">
-        <v>9144</v>
-      </c>
-      <c r="E6">
-        <v>41</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>33</v>
-      </c>
-      <c r="H6">
-        <v>204</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>27</v>
-      </c>
-      <c r="K6">
-        <v>78</v>
-      </c>
-      <c r="L6">
-        <v>23</v>
-      </c>
-      <c r="M6">
-        <v>0.28866799999999998</v>
-      </c>
-      <c r="N6">
-        <v>0.34027000000000002</v>
-      </c>
-      <c r="O6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>1598</v>
-      </c>
-      <c r="C7">
-        <v>668</v>
-      </c>
-      <c r="D7">
-        <v>13711</v>
-      </c>
-      <c r="E7">
-        <v>71</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>205</v>
-      </c>
-      <c r="I7">
-        <v>117</v>
-      </c>
-      <c r="J7">
-        <v>26</v>
-      </c>
-      <c r="K7">
-        <v>148</v>
-      </c>
-      <c r="L7">
-        <v>14</v>
-      </c>
-      <c r="M7">
-        <v>9.7470000000000001E-2</v>
-      </c>
-      <c r="N7">
-        <v>0.17787</v>
-      </c>
-      <c r="O7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
-        <v>1200</v>
-      </c>
-      <c r="C8">
-        <v>402</v>
-      </c>
-      <c r="D8">
-        <v>9603</v>
-      </c>
-      <c r="E8">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>40</v>
-      </c>
-      <c r="H8">
-        <v>189</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>89</v>
-      </c>
-      <c r="L8">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>0.36597600000000002</v>
-      </c>
-      <c r="N8">
-        <v>0.17280000000000001</v>
-      </c>
-      <c r="O8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>1064</v>
-      </c>
-      <c r="C9">
-        <v>501</v>
-      </c>
-      <c r="D9">
-        <v>9118</v>
-      </c>
-      <c r="E9">
-        <v>31</v>
-      </c>
-      <c r="F9">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>26</v>
-      </c>
-      <c r="H9">
-        <v>201</v>
-      </c>
-      <c r="I9">
-        <v>27</v>
-      </c>
-      <c r="J9">
-        <v>27</v>
-      </c>
-      <c r="K9">
-        <v>87</v>
-      </c>
-      <c r="L9">
-        <v>22</v>
-      </c>
-      <c r="M9">
-        <v>0.25709399999999999</v>
-      </c>
-      <c r="N9">
-        <v>0.31597999999999998</v>
-      </c>
-      <c r="O9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
-        <v>1078</v>
-      </c>
-      <c r="C10">
-        <v>545</v>
-      </c>
-      <c r="D10">
-        <v>10163</v>
-      </c>
-      <c r="E10">
-        <v>43</v>
-      </c>
-      <c r="F10">
-        <v>19</v>
-      </c>
-      <c r="G10">
-        <v>26</v>
-      </c>
-      <c r="H10">
-        <v>209</v>
-      </c>
-      <c r="I10">
-        <v>32</v>
-      </c>
-      <c r="J10">
-        <v>19</v>
-      </c>
-      <c r="K10">
-        <v>88</v>
-      </c>
-      <c r="L10">
-        <v>25</v>
-      </c>
-      <c r="M10">
-        <v>0.28670200000000001</v>
-      </c>
-      <c r="N10">
-        <v>0.21953</v>
-      </c>
-      <c r="O10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
-        <v>1051</v>
-      </c>
-      <c r="C11">
-        <v>486</v>
-      </c>
-      <c r="D11">
-        <v>8850</v>
-      </c>
-      <c r="E11">
-        <v>31</v>
-      </c>
-      <c r="F11">
-        <v>19</v>
-      </c>
-      <c r="G11">
-        <v>43</v>
-      </c>
-      <c r="H11">
-        <v>203</v>
-      </c>
-      <c r="I11">
-        <v>24</v>
-      </c>
-      <c r="J11">
-        <v>23</v>
-      </c>
-      <c r="K11">
-        <v>83</v>
-      </c>
-      <c r="L11">
-        <v>23</v>
-      </c>
-      <c r="M11">
-        <v>0.27962100000000001</v>
-      </c>
-      <c r="N11">
-        <v>0.27621000000000001</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>1344</v>
-      </c>
-      <c r="C12">
-        <v>525</v>
-      </c>
-      <c r="D12">
-        <v>11164</v>
-      </c>
-      <c r="E12">
-        <v>59</v>
-      </c>
-      <c r="F12">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>25</v>
-      </c>
-      <c r="H12">
-        <v>172</v>
-      </c>
-      <c r="I12">
-        <v>107</v>
-      </c>
-      <c r="J12">
-        <v>18</v>
-      </c>
-      <c r="K12">
-        <v>131</v>
-      </c>
-      <c r="L12">
-        <v>25</v>
-      </c>
-      <c r="M12">
-        <v>0.18801300000000001</v>
-      </c>
-      <c r="N12">
-        <v>0.13589000000000001</v>
-      </c>
-      <c r="O12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>1285</v>
-      </c>
-      <c r="C13">
-        <v>448</v>
-      </c>
-      <c r="D13">
-        <v>10310</v>
-      </c>
-      <c r="E13">
-        <v>48</v>
-      </c>
-      <c r="F13">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>33</v>
-      </c>
-      <c r="H13">
-        <v>166</v>
-      </c>
-      <c r="I13">
-        <v>105</v>
-      </c>
-      <c r="J13">
-        <v>23</v>
-      </c>
-      <c r="K13">
-        <v>133</v>
-      </c>
-      <c r="L13">
-        <v>24</v>
-      </c>
-      <c r="M13">
-        <v>0.18320600000000001</v>
-      </c>
-      <c r="N13">
-        <v>0.17241000000000001</v>
-      </c>
-      <c r="O13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14">
-        <v>1067</v>
-      </c>
-      <c r="C14">
-        <v>507</v>
-      </c>
-      <c r="D14">
-        <v>8729</v>
-      </c>
-      <c r="E14">
-        <v>28</v>
-      </c>
-      <c r="F14">
-        <v>15</v>
-      </c>
-      <c r="G14">
-        <v>33</v>
-      </c>
-      <c r="H14">
-        <v>201</v>
-      </c>
-      <c r="I14">
-        <v>26</v>
-      </c>
-      <c r="J14">
-        <v>27</v>
-      </c>
-      <c r="K14">
-        <v>84</v>
-      </c>
-      <c r="L14">
-        <v>18</v>
-      </c>
-      <c r="M14">
-        <v>0.217807</v>
-      </c>
-      <c r="N14">
-        <v>0.32493</v>
-      </c>
-      <c r="O14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15">
-        <v>1080</v>
-      </c>
-      <c r="C15">
-        <v>523</v>
-      </c>
-      <c r="D15">
-        <v>8514</v>
-      </c>
-      <c r="E15">
-        <v>31</v>
-      </c>
-      <c r="F15">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>9</v>
-      </c>
-      <c r="H15">
-        <v>194</v>
-      </c>
-      <c r="I15">
-        <v>28</v>
-      </c>
-      <c r="J15">
-        <v>22</v>
-      </c>
-      <c r="K15">
-        <v>77</v>
-      </c>
-      <c r="L15">
-        <v>15</v>
-      </c>
-      <c r="M15">
-        <v>0.20014299999999999</v>
-      </c>
-      <c r="N15">
-        <v>0.27987000000000001</v>
-      </c>
-      <c r="O15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16">
-        <v>1323</v>
-      </c>
-      <c r="C16">
-        <v>625</v>
-      </c>
-      <c r="D16">
-        <v>12079</v>
-      </c>
-      <c r="E16">
-        <v>55</v>
-      </c>
-      <c r="F16">
-        <v>18</v>
-      </c>
-      <c r="G16">
-        <v>38</v>
-      </c>
-      <c r="H16">
-        <v>188</v>
-      </c>
-      <c r="I16">
-        <v>114</v>
-      </c>
-      <c r="J16">
-        <v>27</v>
-      </c>
-      <c r="K16">
-        <v>140</v>
-      </c>
-      <c r="L16">
-        <v>18</v>
-      </c>
-      <c r="M16">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="N16">
-        <v>0.19184000000000001</v>
-      </c>
-      <c r="O16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17">
-        <v>1117</v>
-      </c>
-      <c r="C17">
-        <v>489</v>
-      </c>
-      <c r="D17">
-        <v>9202</v>
-      </c>
-      <c r="E17">
-        <v>35</v>
-      </c>
-      <c r="F17">
-        <v>19</v>
-      </c>
-      <c r="G17">
-        <v>43</v>
-      </c>
-      <c r="H17">
-        <v>208</v>
-      </c>
-      <c r="I17">
-        <v>25</v>
-      </c>
-      <c r="J17">
-        <v>17</v>
-      </c>
-      <c r="K17">
-        <v>74</v>
-      </c>
-      <c r="L17">
-        <v>28</v>
-      </c>
-      <c r="M17">
-        <v>0.37192199999999997</v>
-      </c>
-      <c r="N17">
-        <v>0.22897000000000001</v>
-      </c>
-      <c r="O17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18">
-        <v>1122</v>
-      </c>
-      <c r="C18">
-        <v>572</v>
-      </c>
-      <c r="D18">
-        <v>10503</v>
-      </c>
-      <c r="E18">
-        <v>50</v>
-      </c>
-      <c r="F18">
-        <v>17</v>
-      </c>
-      <c r="G18">
-        <v>36</v>
-      </c>
-      <c r="H18">
-        <v>163</v>
-      </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
-      <c r="J18">
-        <v>17</v>
-      </c>
-      <c r="K18">
-        <v>139</v>
-      </c>
-      <c r="L18">
-        <v>18</v>
-      </c>
-      <c r="M18">
-        <v>0.13261999999999999</v>
-      </c>
-      <c r="N18">
-        <v>0.1225</v>
-      </c>
-      <c r="O18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19">
-        <v>1077</v>
-      </c>
-      <c r="C19">
-        <v>636</v>
-      </c>
-      <c r="D19">
-        <v>10028</v>
-      </c>
-      <c r="E19">
-        <v>43</v>
-      </c>
-      <c r="F19">
-        <v>21</v>
-      </c>
-      <c r="G19">
-        <v>37</v>
-      </c>
-      <c r="H19">
-        <v>218</v>
-      </c>
-      <c r="I19">
-        <v>27</v>
-      </c>
-      <c r="J19">
-        <v>24</v>
-      </c>
-      <c r="K19">
-        <v>90</v>
-      </c>
-      <c r="L19">
-        <v>29</v>
-      </c>
-      <c r="M19">
-        <v>0.324349</v>
-      </c>
-      <c r="N19">
-        <v>0.26940999999999998</v>
-      </c>
-      <c r="O19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20">
-        <v>1076</v>
-      </c>
-      <c r="C20">
-        <v>504</v>
-      </c>
-      <c r="D20">
-        <v>8790</v>
-      </c>
-      <c r="E20">
-        <v>31</v>
-      </c>
-      <c r="F20">
-        <v>19</v>
-      </c>
-      <c r="G20">
-        <v>27</v>
-      </c>
-      <c r="H20">
-        <v>198</v>
-      </c>
-      <c r="I20">
-        <v>21</v>
-      </c>
-      <c r="J20">
-        <v>19</v>
-      </c>
-      <c r="K20">
-        <v>90</v>
-      </c>
-      <c r="L20">
-        <v>27</v>
-      </c>
-      <c r="M20">
-        <v>0.30358200000000002</v>
-      </c>
-      <c r="N20">
-        <v>0.21406</v>
-      </c>
-      <c r="O20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21">
-        <v>1404</v>
-      </c>
-      <c r="C21">
-        <v>654</v>
-      </c>
-      <c r="D21">
-        <v>12974</v>
-      </c>
-      <c r="E21">
-        <v>56</v>
-      </c>
-      <c r="F21">
-        <v>23</v>
-      </c>
-      <c r="G21">
-        <v>23</v>
-      </c>
-      <c r="H21">
-        <v>198</v>
-      </c>
-      <c r="I21">
-        <v>114</v>
-      </c>
-      <c r="J21">
-        <v>17</v>
-      </c>
-      <c r="K21">
-        <v>155</v>
-      </c>
-      <c r="L21">
-        <v>23</v>
-      </c>
-      <c r="M21">
-        <v>0.147928</v>
-      </c>
-      <c r="N21">
-        <v>0.10920000000000001</v>
-      </c>
-      <c r="O21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22">
-        <v>1282</v>
-      </c>
-      <c r="C22">
-        <v>735</v>
-      </c>
-      <c r="D22">
-        <v>10925</v>
-      </c>
-      <c r="E22">
-        <v>42</v>
-      </c>
-      <c r="F22">
-        <v>26</v>
-      </c>
-      <c r="G22">
-        <v>24</v>
-      </c>
-      <c r="H22">
-        <v>245</v>
-      </c>
-      <c r="I22">
-        <v>21</v>
-      </c>
-      <c r="J22">
-        <v>27</v>
-      </c>
-      <c r="K22">
-        <v>91</v>
-      </c>
-      <c r="L22">
-        <v>29</v>
-      </c>
-      <c r="M22">
-        <v>0.32323200000000002</v>
-      </c>
-      <c r="N22">
-        <v>0.29715000000000003</v>
-      </c>
-      <c r="O22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23">
-        <v>1063</v>
-      </c>
-      <c r="C23">
-        <v>487</v>
-      </c>
-      <c r="D23">
-        <v>8294</v>
-      </c>
-      <c r="E23">
-        <v>27</v>
-      </c>
-      <c r="F23">
-        <v>18</v>
-      </c>
-      <c r="G23">
-        <v>31</v>
-      </c>
-      <c r="H23">
-        <v>193</v>
-      </c>
-      <c r="I23">
-        <v>25</v>
-      </c>
-      <c r="J23">
-        <v>22</v>
-      </c>
-      <c r="K23">
-        <v>81</v>
-      </c>
-      <c r="L23">
-        <v>20</v>
-      </c>
-      <c r="M23">
-        <v>0.24251500000000001</v>
-      </c>
-      <c r="N23">
-        <v>0.2651</v>
-      </c>
-      <c r="O23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24">
-        <v>1095</v>
-      </c>
-      <c r="C24">
-        <v>456</v>
-      </c>
-      <c r="D24">
-        <v>8408</v>
-      </c>
-      <c r="E24">
-        <v>28</v>
-      </c>
-      <c r="F24">
-        <v>18</v>
-      </c>
-      <c r="G24">
-        <v>23</v>
-      </c>
-      <c r="H24">
-        <v>199</v>
-      </c>
-      <c r="I24">
-        <v>17</v>
-      </c>
-      <c r="J24">
-        <v>23</v>
-      </c>
-      <c r="K24">
-        <v>73</v>
-      </c>
-      <c r="L24">
-        <v>26</v>
-      </c>
-      <c r="M24">
-        <v>0.36020400000000002</v>
-      </c>
-      <c r="N24">
-        <v>0.30947999999999998</v>
-      </c>
-      <c r="O24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25">
-        <v>1191</v>
-      </c>
-      <c r="C25">
-        <v>588</v>
-      </c>
-      <c r="D25">
-        <v>10166</v>
-      </c>
-      <c r="E25">
-        <v>35</v>
-      </c>
-      <c r="F25">
-        <v>26</v>
-      </c>
-      <c r="G25">
-        <v>28</v>
-      </c>
-      <c r="H25">
-        <v>233</v>
-      </c>
-      <c r="I25">
-        <v>28</v>
-      </c>
-      <c r="J25">
-        <v>24</v>
-      </c>
-      <c r="K25">
-        <v>92</v>
-      </c>
-      <c r="L25">
-        <v>24</v>
-      </c>
-      <c r="M25">
-        <v>0.265158</v>
-      </c>
-      <c r="N25">
-        <v>0.25802999999999998</v>
-      </c>
-      <c r="O25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26">
-        <v>1286</v>
-      </c>
-      <c r="C26">
-        <v>462</v>
-      </c>
-      <c r="D26">
-        <v>8652</v>
-      </c>
-      <c r="E26">
-        <v>40</v>
-      </c>
-      <c r="F26">
-        <v>22</v>
-      </c>
-      <c r="G26">
-        <v>30</v>
-      </c>
-      <c r="H26">
-        <v>191</v>
-      </c>
-      <c r="I26">
-        <v>25</v>
-      </c>
-      <c r="J26">
-        <v>27</v>
-      </c>
-      <c r="K26">
-        <v>78</v>
-      </c>
-      <c r="L26">
-        <v>12</v>
-      </c>
-      <c r="M26">
-        <v>0.155027</v>
-      </c>
-      <c r="N26">
-        <v>0.34092</v>
-      </c>
-      <c r="O26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27">
-        <v>1085</v>
-      </c>
-      <c r="C27">
-        <v>533</v>
-      </c>
-      <c r="D27">
-        <v>8930</v>
-      </c>
-      <c r="E27">
-        <v>36</v>
-      </c>
-      <c r="F27">
-        <v>21</v>
-      </c>
-      <c r="G27">
-        <v>30</v>
-      </c>
-      <c r="H27">
-        <v>192</v>
-      </c>
-      <c r="I27">
-        <v>27</v>
-      </c>
-      <c r="J27">
-        <v>24</v>
-      </c>
-      <c r="K27">
-        <v>89</v>
-      </c>
-      <c r="L27">
-        <v>20</v>
-      </c>
-      <c r="M27">
-        <v>0.230132</v>
-      </c>
-      <c r="N27">
-        <v>0.26972000000000002</v>
-      </c>
-      <c r="O27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28">
-        <v>1296</v>
-      </c>
-      <c r="C28">
-        <v>532</v>
-      </c>
-      <c r="D28">
-        <v>10620</v>
-      </c>
-      <c r="E28">
-        <v>52</v>
-      </c>
-      <c r="F28">
-        <v>18</v>
-      </c>
-      <c r="G28">
-        <v>14</v>
-      </c>
-      <c r="H28">
-        <v>156</v>
-      </c>
-      <c r="I28">
-        <v>107</v>
-      </c>
-      <c r="J28">
-        <v>18</v>
-      </c>
-      <c r="K28">
-        <v>126</v>
-      </c>
-      <c r="L28">
-        <v>16</v>
-      </c>
-      <c r="M28">
-        <v>0.123298</v>
-      </c>
-      <c r="N28">
-        <v>0.13943</v>
-      </c>
-      <c r="O28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29">
-        <v>1422</v>
-      </c>
-      <c r="C29">
-        <v>517</v>
-      </c>
-      <c r="D29">
-        <v>12226</v>
-      </c>
-      <c r="E29">
-        <v>60</v>
-      </c>
-      <c r="F29">
-        <v>21</v>
-      </c>
-      <c r="G29">
-        <v>35</v>
-      </c>
-      <c r="H29">
-        <v>185</v>
-      </c>
-      <c r="I29">
-        <v>120</v>
-      </c>
-      <c r="J29">
-        <v>16</v>
-      </c>
-      <c r="K29">
-        <v>140</v>
-      </c>
-      <c r="L29">
-        <v>9</v>
-      </c>
-      <c r="M29">
-        <v>6.0914000000000003E-2</v>
-      </c>
-      <c r="N29">
-        <v>0.11136</v>
-      </c>
-      <c r="O29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30">
-        <v>1239</v>
-      </c>
-      <c r="C30">
-        <v>486</v>
-      </c>
-      <c r="D30">
-        <v>10570</v>
-      </c>
-      <c r="E30">
-        <v>46</v>
-      </c>
-      <c r="F30">
-        <v>16</v>
-      </c>
-      <c r="G30">
-        <v>46</v>
-      </c>
-      <c r="H30">
-        <v>162</v>
-      </c>
-      <c r="I30">
-        <v>100</v>
-      </c>
-      <c r="J30">
-        <v>17</v>
-      </c>
-      <c r="K30">
-        <v>127</v>
-      </c>
-      <c r="L30">
-        <v>17</v>
-      </c>
-      <c r="M30">
-        <v>0.132717</v>
-      </c>
-      <c r="N30">
-        <v>0.1338</v>
-      </c>
-      <c r="O30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31">
-        <v>1760</v>
-      </c>
-      <c r="C31">
-        <v>518</v>
-      </c>
-      <c r="D31">
-        <v>10817</v>
-      </c>
-      <c r="E31">
-        <v>46</v>
-      </c>
-      <c r="F31">
-        <v>21</v>
-      </c>
-      <c r="G31">
-        <v>39</v>
-      </c>
-      <c r="H31">
-        <v>173</v>
-      </c>
-      <c r="I31">
-        <v>106</v>
-      </c>
-      <c r="J31">
-        <v>14</v>
-      </c>
-      <c r="K31">
-        <v>134</v>
-      </c>
-      <c r="L31">
-        <v>20</v>
-      </c>
-      <c r="M31">
-        <v>0.14706900000000001</v>
-      </c>
-      <c r="N31">
-        <v>0.1028</v>
-      </c>
-      <c r="O31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32">
-        <v>1051</v>
-      </c>
-      <c r="C32">
-        <v>541</v>
-      </c>
-      <c r="D32">
-        <v>9101</v>
-      </c>
-      <c r="E32">
-        <v>36</v>
-      </c>
-      <c r="F32">
-        <v>20</v>
-      </c>
-      <c r="G32">
-        <v>14</v>
-      </c>
-      <c r="H32">
-        <v>199</v>
-      </c>
-      <c r="I32">
-        <v>27</v>
-      </c>
-      <c r="J32">
-        <v>22</v>
-      </c>
-      <c r="K32">
-        <v>92</v>
-      </c>
-      <c r="L32">
-        <v>20</v>
-      </c>
-      <c r="M32">
-        <v>0.21924099999999999</v>
-      </c>
-      <c r="N32">
-        <v>0.23776</v>
-      </c>
-      <c r="O32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33">
-        <v>1227</v>
-      </c>
-      <c r="C33">
-        <v>454</v>
-      </c>
-      <c r="D33">
-        <v>10121</v>
-      </c>
-      <c r="E33">
-        <v>39</v>
-      </c>
-      <c r="F33">
-        <v>18</v>
-      </c>
-      <c r="G33">
-        <v>28</v>
-      </c>
-      <c r="H33">
-        <v>158</v>
-      </c>
-      <c r="I33">
-        <v>101</v>
-      </c>
-      <c r="J33">
-        <v>15</v>
-      </c>
-      <c r="K33">
-        <v>137</v>
-      </c>
-      <c r="L33">
-        <v>26</v>
-      </c>
-      <c r="M33">
-        <v>0.19034499999999999</v>
-      </c>
-      <c r="N33">
-        <v>0.1099</v>
-      </c>
-      <c r="O33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34">
-        <v>1308</v>
-      </c>
-      <c r="C34">
-        <v>537</v>
-      </c>
-      <c r="D34">
-        <v>11315</v>
-      </c>
-      <c r="E34">
-        <v>47</v>
-      </c>
-      <c r="F34">
-        <v>22</v>
-      </c>
-      <c r="G34">
-        <v>30</v>
-      </c>
-      <c r="H34">
-        <v>169</v>
-      </c>
-      <c r="I34">
-        <v>115</v>
-      </c>
-      <c r="J34">
-        <v>24</v>
-      </c>
-      <c r="K34">
-        <v>139</v>
-      </c>
-      <c r="L34">
-        <v>19</v>
-      </c>
-      <c r="M34">
-        <v>0.13414999999999999</v>
-      </c>
-      <c r="N34">
-        <v>0.16905000000000001</v>
-      </c>
-      <c r="O34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35">
-        <v>1073</v>
-      </c>
-      <c r="C35">
-        <v>443</v>
-      </c>
-      <c r="D35">
-        <v>8427</v>
-      </c>
-      <c r="E35">
-        <v>25</v>
-      </c>
-      <c r="F35">
-        <v>13</v>
-      </c>
-      <c r="G35">
-        <v>26</v>
-      </c>
-      <c r="H35">
-        <v>203</v>
-      </c>
-      <c r="I35">
-        <v>25</v>
-      </c>
-      <c r="J35">
-        <v>13</v>
-      </c>
-      <c r="K35">
-        <v>79</v>
-      </c>
-      <c r="L35">
-        <v>35</v>
-      </c>
-      <c r="M35">
-        <v>0.44720199999999999</v>
-      </c>
-      <c r="N35">
-        <v>0.16594999999999999</v>
-      </c>
-      <c r="O35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36">
-        <v>1095</v>
-      </c>
-      <c r="C36">
-        <v>495</v>
-      </c>
-      <c r="D36">
-        <v>8768</v>
-      </c>
-      <c r="E36">
-        <v>34</v>
-      </c>
-      <c r="F36">
-        <v>15</v>
-      </c>
-      <c r="G36">
-        <v>34</v>
-      </c>
-      <c r="H36">
-        <v>215</v>
-      </c>
-      <c r="I36">
-        <v>20</v>
-      </c>
-      <c r="J36">
-        <v>25</v>
-      </c>
-      <c r="K36">
-        <v>75</v>
-      </c>
-      <c r="L36">
-        <v>28</v>
-      </c>
-      <c r="M36">
-        <v>0.37734299999999998</v>
-      </c>
-      <c r="N36">
-        <v>0.32945999999999998</v>
-      </c>
-      <c r="O36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37">
-        <v>1232</v>
-      </c>
-      <c r="C37">
-        <v>527</v>
-      </c>
-      <c r="D37">
-        <v>10839</v>
-      </c>
-      <c r="E37">
-        <v>49</v>
-      </c>
-      <c r="F37">
-        <v>19</v>
-      </c>
-      <c r="G37">
-        <v>37</v>
-      </c>
-      <c r="H37">
-        <v>176</v>
-      </c>
-      <c r="I37">
-        <v>109</v>
-      </c>
-      <c r="J37">
-        <v>18</v>
-      </c>
-      <c r="K37">
-        <v>132</v>
-      </c>
-      <c r="L37">
-        <v>22</v>
-      </c>
-      <c r="M37">
-        <v>0.16368099999999999</v>
-      </c>
-      <c r="N37">
-        <v>0.13274</v>
-      </c>
-      <c r="O37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38">
-        <v>1231</v>
-      </c>
-      <c r="C38">
-        <v>465</v>
-      </c>
-      <c r="D38">
-        <v>10331</v>
-      </c>
-      <c r="E38">
-        <v>57</v>
-      </c>
-      <c r="F38">
-        <v>13</v>
-      </c>
-      <c r="G38">
-        <v>24</v>
-      </c>
-      <c r="H38">
-        <v>167</v>
-      </c>
-      <c r="I38">
-        <v>99</v>
-      </c>
-      <c r="J38">
-        <v>19</v>
-      </c>
-      <c r="K38">
-        <v>140</v>
-      </c>
-      <c r="L38">
-        <v>20</v>
-      </c>
-      <c r="M38">
-        <v>0.14396500000000001</v>
-      </c>
-      <c r="N38">
-        <v>0.13397000000000001</v>
-      </c>
-      <c r="O38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39">
-        <v>1190</v>
-      </c>
-      <c r="C39">
-        <v>543</v>
-      </c>
-      <c r="D39">
-        <v>9368</v>
-      </c>
-      <c r="E39">
-        <v>39</v>
-      </c>
-      <c r="F39">
-        <v>25</v>
-      </c>
-      <c r="G39">
-        <v>39</v>
-      </c>
-      <c r="H39">
-        <v>226</v>
-      </c>
-      <c r="I39">
-        <v>22</v>
-      </c>
-      <c r="J39">
-        <v>16</v>
-      </c>
-      <c r="K39">
-        <v>85</v>
-      </c>
-      <c r="L39">
-        <v>29</v>
-      </c>
-      <c r="M39">
-        <v>0.34019300000000002</v>
-      </c>
-      <c r="N39">
-        <v>0.19147</v>
-      </c>
-      <c r="O39" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40">
-        <v>1433</v>
-      </c>
-      <c r="C40">
-        <v>501</v>
-      </c>
-      <c r="D40">
-        <v>10160</v>
-      </c>
-      <c r="E40">
-        <v>55</v>
-      </c>
-      <c r="F40">
-        <v>19</v>
-      </c>
-      <c r="G40">
-        <v>28</v>
-      </c>
-      <c r="H40">
-        <v>159</v>
-      </c>
-      <c r="I40">
-        <v>104</v>
-      </c>
-      <c r="J40">
-        <v>23</v>
-      </c>
-      <c r="K40">
-        <v>129</v>
-      </c>
-      <c r="L40">
-        <v>20</v>
-      </c>
-      <c r="M40">
-        <v>0.15903600000000001</v>
-      </c>
-      <c r="N40">
-        <v>0.17838999999999999</v>
-      </c>
-      <c r="O40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41">
-        <v>1025</v>
-      </c>
-      <c r="C41">
-        <v>416</v>
-      </c>
-      <c r="D41">
-        <v>7334</v>
-      </c>
-      <c r="E41">
-        <v>29</v>
-      </c>
-      <c r="F41">
-        <v>13</v>
-      </c>
-      <c r="G41">
-        <v>29</v>
-      </c>
-      <c r="H41">
-        <v>167</v>
-      </c>
-      <c r="I41">
-        <v>18</v>
-      </c>
-      <c r="J41">
-        <v>19</v>
-      </c>
-      <c r="K41">
-        <v>77</v>
-      </c>
-      <c r="L41">
-        <v>17</v>
-      </c>
-      <c r="M41">
-        <v>0.222825</v>
-      </c>
-      <c r="N41">
-        <v>0.24248</v>
-      </c>
-      <c r="O41" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42">
-        <v>1058</v>
-      </c>
-      <c r="C42">
-        <v>524</v>
-      </c>
-      <c r="D42">
-        <v>8624</v>
-      </c>
-      <c r="E42">
-        <v>29</v>
-      </c>
-      <c r="F42">
-        <v>19</v>
-      </c>
-      <c r="G42">
-        <v>41</v>
-      </c>
-      <c r="H42">
-        <v>202</v>
-      </c>
-      <c r="I42">
-        <v>25</v>
-      </c>
-      <c r="J42">
-        <v>20</v>
-      </c>
-      <c r="K42">
-        <v>85</v>
-      </c>
-      <c r="L42">
-        <v>27</v>
-      </c>
-      <c r="M42">
-        <v>0.318913</v>
-      </c>
-      <c r="N42">
-        <v>0.24056</v>
-      </c>
-      <c r="O42" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43">
-        <v>1036</v>
-      </c>
-      <c r="C43">
-        <v>472</v>
-      </c>
-      <c r="D43">
-        <v>8644</v>
-      </c>
-      <c r="E43">
-        <v>43</v>
-      </c>
-      <c r="F43">
-        <v>15</v>
-      </c>
-      <c r="G43">
-        <v>36</v>
-      </c>
-      <c r="H43">
-        <v>201</v>
-      </c>
-      <c r="I43">
-        <v>23</v>
-      </c>
-      <c r="J43">
-        <v>19</v>
-      </c>
-      <c r="K43">
-        <v>80</v>
-      </c>
-      <c r="L43">
-        <v>23</v>
-      </c>
-      <c r="M43">
-        <v>0.28834599999999999</v>
-      </c>
-      <c r="N43">
-        <v>0.24192</v>
-      </c>
-      <c r="O43" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" t="s">
-        <v>61</v>
-      </c>
-      <c r="D48" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" t="s">
-        <v>63</v>
-      </c>
-      <c r="F48" t="s">
-        <v>64</v>
-      </c>
-      <c r="G48" t="s">
-        <v>65</v>
-      </c>
-      <c r="H48" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50">
-        <v>25</v>
-      </c>
-      <c r="D50">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51">
-        <v>9000</v>
-      </c>
-      <c r="D51">
-        <v>11100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>5</v>
-      </c>
-      <c r="B52" t="s">
-        <v>68</v>
-      </c>
-      <c r="C52">
-        <v>17</v>
-      </c>
-      <c r="D52">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>2</v>
-      </c>
-      <c r="B53" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53">
-        <v>510</v>
-      </c>
-      <c r="D53">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" t="s">
-        <v>68</v>
-      </c>
-      <c r="C54">
-        <v>24</v>
-      </c>
-      <c r="D54">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" t="s">
-        <v>68</v>
-      </c>
-      <c r="C55">
-        <v>204</v>
-      </c>
-      <c r="D55">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>8</v>
-      </c>
-      <c r="B56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56">
-        <v>24</v>
-      </c>
-      <c r="D56">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57">
-        <v>30</v>
-      </c>
-      <c r="D57">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>1</v>
-      </c>
-      <c r="B58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58">
-        <v>1120</v>
-      </c>
-      <c r="D58">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59">
-        <v>22</v>
-      </c>
-      <c r="D59">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60">
-        <v>35</v>
-      </c>
-      <c r="D60">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B61" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61">
-        <v>83</v>
-      </c>
-      <c r="D61">
-        <v>137</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18244,7 +18006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19694,7 +19456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22534,7 +22296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22829,7 +22591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23998,7 +23760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Q122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -29901,7 +29663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -30704,4 +30466,232 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>899</v>
+      </c>
+      <c r="C1" t="s">
+        <v>900</v>
+      </c>
+      <c r="D1" t="s">
+        <v>901</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>902</v>
+      </c>
+      <c r="B2">
+        <v>23</v>
+      </c>
+      <c r="C2">
+        <v>22.9</v>
+      </c>
+      <c r="D2">
+        <v>22.9</v>
+      </c>
+      <c r="E2">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>903</v>
+      </c>
+      <c r="B3">
+        <v>0.159</v>
+      </c>
+      <c r="C3">
+        <v>0.16</v>
+      </c>
+      <c r="D3">
+        <v>0.16</v>
+      </c>
+      <c r="E3">
+        <v>0.54500000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>904</v>
+      </c>
+      <c r="B4">
+        <v>2.35</v>
+      </c>
+      <c r="C4">
+        <v>2.34</v>
+      </c>
+      <c r="D4">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E4">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>905</v>
+      </c>
+      <c r="B5">
+        <v>1.96</v>
+      </c>
+      <c r="C5">
+        <v>1.94</v>
+      </c>
+      <c r="D5">
+        <v>1.97</v>
+      </c>
+      <c r="E5">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>906</v>
+      </c>
+      <c r="B6">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="C6">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="D6">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="E6">
+        <v>0.88400000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>907</v>
+      </c>
+      <c r="B7">
+        <v>3.19</v>
+      </c>
+      <c r="C7">
+        <v>3.2</v>
+      </c>
+      <c r="D7">
+        <v>3.22</v>
+      </c>
+      <c r="E7">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>908</v>
+      </c>
+      <c r="B8">
+        <v>23.2</v>
+      </c>
+      <c r="C8">
+        <v>22.4</v>
+      </c>
+      <c r="D8">
+        <v>22.9</v>
+      </c>
+      <c r="E8">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>909</v>
+      </c>
+      <c r="B9">
+        <v>7.69</v>
+      </c>
+      <c r="C9">
+        <v>7.76</v>
+      </c>
+      <c r="D9">
+        <v>7.76</v>
+      </c>
+      <c r="E9">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>2.93</v>
+      </c>
+      <c r="D10">
+        <v>2.99</v>
+      </c>
+      <c r="E10">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>911</v>
+      </c>
+      <c r="B11">
+        <v>7.95</v>
+      </c>
+      <c r="C11">
+        <v>7.78</v>
+      </c>
+      <c r="D11">
+        <v>7.97</v>
+      </c>
+      <c r="E11">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>912</v>
+      </c>
+      <c r="B12">
+        <v>1.96</v>
+      </c>
+      <c r="C12">
+        <v>1.96</v>
+      </c>
+      <c r="D12">
+        <v>1.91</v>
+      </c>
+      <c r="E12">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>913</v>
+      </c>
+      <c r="B13">
+        <v>159</v>
+      </c>
+      <c r="C13">
+        <v>152</v>
+      </c>
+      <c r="D13">
+        <v>160</v>
+      </c>
+      <c r="E13">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>